--- a/VerveStacks_THA_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_THA_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_THA_grids_kan\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4EF16BE0-32E9-4BF5-8924-F6142250ADEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F75DE6D7-91BB-4477-96D4-95A0956C4F92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{0733F4AC-10E1-4D61-B808-3E9C889399B8}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{754B0EEE-90C7-40C6-B856-279029805F2C}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -2246,7 +2246,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFE92E78-F8A3-48EA-94AD-EC549829218D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2E720E9-B1A4-4116-9F34-46BF1B67BF95}">
   <dimension ref="B3:L252"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
